--- a/NuevasNotas/Vespertina/Resultados_Auditoria_Notas/Matriz_Marcada_7BV.xlsx
+++ b/NuevasNotas/Vespertina/Resultados_Auditoria_Notas/Matriz_Marcada_7BV.xlsx
@@ -2,53 +2,63 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN DISCREPANCIAS" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Matriz Final Séptimo B" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <color indexed="8"/>
       <sz val="11"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <color indexed="8"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color indexed="8"/>
+      <sz val="15"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color indexed="8"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color indexed="8"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color indexed="9"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color indexed="8"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
+      <color indexed="8"/>
       <sz val="9"/>
     </font>
     <font>
@@ -58,7 +68,14 @@
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00065F46"/>
     </font>
   </fonts>
   <fills count="7">
@@ -69,7 +86,16 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="solid"/>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="8"/>
+        <bgColor auto="1"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -79,24 +105,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E7EB"/>
-        <bgColor rgb="00E5E7EB"/>
+        <fgColor rgb="003B82F6"/>
+        <bgColor rgb="003B82F6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3F4F6"/>
-        <bgColor rgb="00F3F4F6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -106,23 +126,99 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00000000"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color rgb="00000000"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color rgb="00000000"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color rgb="00000000"/>
+        <color indexed="10"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00000000"/>
+        <color indexed="8"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -130,10 +226,10 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00000000"/>
+        <color indexed="8"/>
       </right>
       <top style="thin">
-        <color rgb="00000000"/>
+        <color indexed="8"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -142,171 +238,183 @@
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00000000"/>
+        <color indexed="8"/>
       </top>
       <bottom style="thin">
-        <color rgb="00000000"/>
+        <color indexed="8"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00000000"/>
+        <color indexed="8"/>
       </right>
       <top style="thin">
-        <color rgb="00000000"/>
+        <color indexed="8"/>
       </top>
       <bottom style="thin">
-        <color rgb="00000000"/>
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="26">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
+      <rgbColor rgb="ffff0000"/>
+      <rgbColor rgb="ff00ff00"/>
+      <rgbColor rgb="ff0000ff"/>
+      <rgbColor rgb="ffffff00"/>
+      <rgbColor rgb="ffff00ff"/>
+      <rgbColor rgb="ff00ffff"/>
+      <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
+      <rgbColor rgb="ffaaaaaa"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office Theme">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="A7A7A7"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="535353"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="4F81BD"/>
@@ -330,80 +438,22 @@
         <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="FF00FF"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office Theme">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Helvetica Neue"/>
+        <a:ea typeface="Helvetica Neue"/>
+        <a:cs typeface="Helvetica Neue"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Helvetica Neue"/>
+        <a:ea typeface="Helvetica Neue"/>
+        <a:cs typeface="Helvetica Neue"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office Theme">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -435,20 +485,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="129999"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -460,7 +506,7 @@
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
-              <a:satMod val="105000"/>
+              <a:satMod val="104999"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
@@ -481,16 +527,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -499,23 +536,21 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -570,8 +605,852 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="25400" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
+            <a:srgbClr val="000000">
+              <a:alpha val="35000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:sp3d/>
+      </a:spPr>
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+        <a:spAutoFit/>
+      </a:bodyPr>
+      <a:lstStyle>
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:defRPr>
+        </a:defPPr>
+        <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl1pPr>
+        <a:lvl2pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl2pPr>
+        <a:lvl3pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl3pPr>
+        <a:lvl4pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl4pPr>
+        <a:lvl5pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl5pPr>
+        <a:lvl6pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl6pPr>
+        <a:lvl7pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl7pPr>
+        <a:lvl8pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl8pPr>
+        <a:lvl9pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl9pPr>
+      </a:lstStyle>
+      <a:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="none"/>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr>
+        <a:noFill/>
+        <a:ln w="25400" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+            <a:srgbClr val="000000">
+              <a:alpha val="38000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:sp3d/>
+      </a:spPr>
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+        <a:noAutofit/>
+      </a:bodyPr>
+      <a:lstStyle>
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:defPPr>
+        <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl1pPr>
+        <a:lvl2pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl2pPr>
+        <a:lvl3pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl3pPr>
+        <a:lvl4pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl4pPr>
+        <a:lvl5pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl5pPr>
+        <a:lvl6pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl6pPr>
+        <a:lvl7pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl7pPr>
+        <a:lvl8pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl8pPr>
+        <a:lvl9pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl9pPr>
+      </a:lstStyle>
+      <a:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="none"/>
+      </a:style>
+    </a:lnDef>
+    <a:txDef>
+      <a:spPr>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat">
+          <a:noFill/>
+          <a:miter lim="400000"/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </a:spPr>
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+        <a:spAutoFit/>
+      </a:bodyPr>
+      <a:lstStyle>
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:defRPr>
+        </a:defPPr>
+        <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl1pPr>
+        <a:lvl2pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl2pPr>
+        <a:lvl3pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl3pPr>
+        <a:lvl4pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl4pPr>
+        <a:lvl5pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl5pPr>
+        <a:lvl6pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl6pPr>
+        <a:lvl7pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl7pPr>
+        <a:lvl8pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl8pPr>
+        <a:lvl9pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl9pPr>
+      </a:lstStyle>
+      <a:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="none"/>
+      </a:style>
+    </a:txDef>
+  </a:objectDefaults>
 </a:theme>
 </file>
 
@@ -581,402 +1460,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" style="18" min="1" max="1"/>
+    <col width="25" customWidth="1" style="18" min="2" max="2"/>
+    <col width="30" customWidth="1" style="18" min="3" max="3"/>
+    <col width="12" customWidth="1" style="18" min="4" max="4"/>
+    <col width="12" customWidth="1" style="18" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="18">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>RESUMEN DE AUDITORÍA (DISCREPANCIAS ENCONTRADAS)</t>
         </is>
       </c>
-      <c r="B1" s="13" t="n"/>
-      <c r="C1" s="13" t="n"/>
-      <c r="D1" s="13" t="n"/>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Curso</t>
-        </is>
-      </c>
-      <c r="B2" s="14" t="inlineStr">
-        <is>
-          <t>Estudiante</t>
-        </is>
-      </c>
-      <c r="C2" s="14" t="inlineStr">
-        <is>
-          <t>Tipo de Problema</t>
-        </is>
-      </c>
-      <c r="D2" s="14" t="inlineStr">
-        <is>
-          <t>Detalle de la Discrepancia</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>7BV</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>CHILLOGALLI BARRERA ADAMARIS</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>7BV</t>
-        </is>
-      </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>CHILLOGALLI BARRERA ADAMARIS LISHET</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>7BV</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>GUACHICHULLCA SIAVICHAY MATEO</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>7BV</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>GUACHICHULLCA SIAVICHAY MATEO SEBASTIAN</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>7BV</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>GUAMAN PINEDA KELLY ESTEFAN</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="25" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>7BV</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>GUAMAN PINEDA KELLY ESTEFANIA</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="25" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>7BV</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>JIMBO QUISCUALTUD RUBY JULEIDY</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>7BV</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>JIMBO QUISCUALTUD RUBY JULIETH</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>7BV</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>MEJIA ZHINDON BRIGITTE TAMAR</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="25" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>7BV</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>MEJIA ZHINDON BRIGITTE TAMARA</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="25" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>7BV</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>PALMA RODRIGUEZ VICTORIA ANABEL</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="25" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>7BV</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>PALMA RODRIGUEZ VICTORIA ANAHI</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>7BV</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>TENESACA AMENDAÑO CARLOS DAVID</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="25" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>7BV</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>TENESACA AMENDAÑO CARLOS MANUEL</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="25" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>7BV</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>TONGOMBOL CARCHIPULLA MARIA</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="25" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>7BV</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>TONGOMBOL CARCHIPULLA MARIA ELISA</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
+      <c r="B1" s="23" t="n"/>
+      <c r="C1" s="23" t="n"/>
+      <c r="D1" s="23" t="n"/>
+      <c r="E1" s="23" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" s="18">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>▶ CURSO: 7BV</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1" s="18">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>✅ Todo el curso está perfectamente cuadrado. No hay discrepancias.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -989,2312 +1512,2364 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O43"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" style="1" min="1" max="1"/>
+    <col width="13" customWidth="1" style="1" min="2" max="2"/>
+    <col width="38" customWidth="1" style="1" min="3" max="3"/>
+    <col width="7" customWidth="1" style="1" min="4" max="10"/>
+    <col width="11" customWidth="1" style="1" min="11" max="12"/>
+    <col width="10" customWidth="1" style="1" min="13" max="14"/>
+    <col width="13" customWidth="1" style="1" min="15" max="15"/>
+    <col width="8.851559999999999" customWidth="1" style="1" min="16" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="18.5" customHeight="1" s="18">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>UNIDAD EDUCATIVA "ESTADOS UNIDOS DE NORTE AMÉRICA"</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="B1" s="19" t="n"/>
+      <c r="C1" s="19" t="n"/>
+      <c r="D1" s="19" t="n"/>
+      <c r="E1" s="19" t="n"/>
+      <c r="F1" s="19" t="n"/>
+      <c r="G1" s="19" t="n"/>
+      <c r="H1" s="19" t="n"/>
+      <c r="I1" s="19" t="n"/>
+      <c r="J1" s="19" t="n"/>
+      <c r="K1" s="19" t="n"/>
+      <c r="L1" s="19" t="n"/>
+      <c r="M1" s="19" t="n"/>
+      <c r="N1" s="19" t="n"/>
+      <c r="O1" s="20" t="n"/>
+    </row>
+    <row r="2" ht="14.6" customHeight="1" s="18">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>AÑO LECTIVO 2025 - 2026</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="B2" s="19" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="19" t="n"/>
+      <c r="H2" s="19" t="n"/>
+      <c r="I2" s="19" t="n"/>
+      <c r="J2" s="19" t="n"/>
+      <c r="K2" s="19" t="n"/>
+      <c r="L2" s="19" t="n"/>
+      <c r="M2" s="19" t="n"/>
+      <c r="N2" s="19" t="n"/>
+      <c r="O2" s="20" t="n"/>
+    </row>
+    <row r="3" ht="14.6" customHeight="1" s="18">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>MATRIZ FINAL ANUAL</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="B3" s="19" t="n"/>
+      <c r="C3" s="19" t="n"/>
+      <c r="D3" s="19" t="n"/>
+      <c r="E3" s="19" t="n"/>
+      <c r="F3" s="19" t="n"/>
+      <c r="G3" s="19" t="n"/>
+      <c r="H3" s="19" t="n"/>
+      <c r="I3" s="19" t="n"/>
+      <c r="J3" s="19" t="n"/>
+      <c r="K3" s="19" t="n"/>
+      <c r="L3" s="19" t="n"/>
+      <c r="M3" s="19" t="n"/>
+      <c r="N3" s="19" t="n"/>
+      <c r="O3" s="20" t="n"/>
+    </row>
+    <row r="4" ht="13.55" customHeight="1" s="18">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="11.7" customHeight="1" s="18">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>DATOS INFORMATIVOS</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="12" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="B5" s="21" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>TUTOR</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>LIC. YOLANDA MAILA</t>
         </is>
       </c>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="F5" s="21" t="n"/>
+      <c r="G5" s="21" t="n"/>
+      <c r="H5" s="22" t="n"/>
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>AÑO DE BÁSICA</t>
         </is>
       </c>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="J5" s="22" t="n"/>
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>SÉPTIMO B</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
         <is>
           <t>JORNADA</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M5" s="8" t="inlineStr">
         <is>
           <t>VESPERTINA</t>
         </is>
       </c>
-      <c r="N5" s="11" t="n"/>
-      <c r="O5" s="12" t="n"/>
-    </row>
-    <row r="6" ht="120" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="N5" s="21" t="n"/>
+      <c r="O5" s="22" t="n"/>
+    </row>
+    <row r="6" ht="120" customHeight="1" s="18">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>CÉDULA</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>ESTUDIANTES
 APELLIDOS/NOMBRES</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>LENGUA Y
 LITERATURA</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>MATEMÁTICA</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>CIENCIAS
 NATURALES</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>ESTUDIOS
 SOCIALES</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>INGLES</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>EDUCACIÓN
 CULTURAL Y
 ARTÍSTICA</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>EDUCACIÓN
 FÍSICA</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>ANIMACIÓN A LA
 LECTURA</t>
         </is>
       </c>
-      <c r="L6" s="6" t="inlineStr">
+      <c r="L6" s="8" t="inlineStr">
         <is>
           <t>CÍVICA Y
 ACOMPAÑAMIENTO
 INTEGRAL</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="M6" s="12" t="inlineStr">
         <is>
           <t>PROMEDIO</t>
         </is>
       </c>
-      <c r="N6" s="6" t="inlineStr">
+      <c r="N6" s="12" t="inlineStr">
         <is>
           <t>COMPORTAMIENTO</t>
         </is>
       </c>
-      <c r="O6" s="6" t="inlineStr">
+      <c r="O6" s="12" t="inlineStr">
         <is>
           <t>PROMOCIÓN</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="7" t="n">
+    <row r="7" ht="12.7" customHeight="1" s="18">
+      <c r="A7" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>0151000429</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>AVILA BENAVIDES BORIS RENATO</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="16" t="n">
         <v>8.23</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="16" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="16" t="n">
         <v>8.33</v>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="H7" s="16" t="n">
         <v>7.11</v>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" s="16" t="n">
         <v>8.44</v>
       </c>
-      <c r="J7" s="9" t="n">
+      <c r="J7" s="16" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="K7" s="14" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="n">
+      <c r="L7" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M7" s="16" t="n">
         <v>8.07</v>
       </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="N7" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O7" s="7" t="inlineStr">
+      <c r="O7" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="n">
+    <row r="8" ht="12.7" customHeight="1" s="18">
+      <c r="A8" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>01450293350</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>AVILA BERNAL KIMBERLY FERNANDA</t>
         </is>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="16" t="n">
         <v>9.26</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="16" t="n">
         <v>9.35</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="16" t="n">
         <v>8.84</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="16" t="n">
         <v>8.99</v>
       </c>
-      <c r="H8" s="9" t="n">
+      <c r="H8" s="16" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="I8" s="9" t="n">
+      <c r="I8" s="16" t="n">
         <v>9.16</v>
       </c>
-      <c r="J8" s="9" t="n">
+      <c r="J8" s="16" t="n">
         <v>9.42</v>
       </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M8" s="9" t="n">
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M8" s="16" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="N8" s="7" t="inlineStr">
+      <c r="N8" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O8" s="7" t="inlineStr">
+      <c r="O8" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="7" t="n">
+    <row r="9" ht="12.7" customHeight="1" s="18">
+      <c r="A9" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>0151284106</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>CHILLOGALLI BARRERA ADAMARIS</t>
         </is>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="16" t="n">
         <v>8.91</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="16" t="n">
         <v>8.960000000000001</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="16" t="n">
         <v>9.01</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="16" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H9" s="16" t="n">
         <v>9.35</v>
       </c>
-      <c r="I9" s="9" t="n">
+      <c r="I9" s="16" t="n">
         <v>9.48</v>
       </c>
-      <c r="J9" s="9" t="n">
+      <c r="J9" s="16" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M9" s="9" t="n">
+      <c r="K9" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L9" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="n">
         <v>9.140000000000001</v>
       </c>
-      <c r="N9" s="7" t="inlineStr">
+      <c r="N9" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O9" s="7" t="inlineStr">
+      <c r="O9" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="n">
+    <row r="10" ht="12.7" customHeight="1" s="18">
+      <c r="A10" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>0151005261</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>CHIMBO URGILES ZAMIRA ALEXANDRA</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="16" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="16" t="n">
         <v>8.08</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="16" t="n">
         <v>8.83</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="16" t="n">
         <v>8.85</v>
       </c>
-      <c r="H10" s="9" t="n">
+      <c r="H10" s="16" t="n">
         <v>7.6</v>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="I10" s="16" t="n">
         <v>8.6</v>
       </c>
-      <c r="J10" s="9" t="n">
+      <c r="J10" s="16" t="n">
         <v>8.98</v>
       </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L10" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M10" s="9" t="n">
+      <c r="K10" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M10" s="16" t="n">
         <v>8.52</v>
       </c>
-      <c r="N10" s="7" t="inlineStr">
+      <c r="N10" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O10" s="7" t="inlineStr">
+      <c r="O10" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="n">
+    <row r="11" ht="12.7" customHeight="1" s="18">
+      <c r="A11" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>0151278363</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>ELIZALDE MALLA ALEX SEBASTIAN</t>
         </is>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="16" t="n">
         <v>9.039999999999999</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="16" t="n">
         <v>8.77</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="16" t="n">
         <v>9.119999999999999</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="16" t="n">
         <v>9.16</v>
       </c>
-      <c r="H11" s="9" t="n">
+      <c r="H11" s="16" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="I11" s="16" t="n">
         <v>9.16</v>
       </c>
-      <c r="J11" s="9" t="n">
+      <c r="J11" s="16" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M11" s="9" t="n">
+      <c r="K11" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="n">
         <v>9.109999999999999</v>
       </c>
-      <c r="N11" s="7" t="inlineStr">
+      <c r="N11" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O11" s="7" t="inlineStr">
+      <c r="O11" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="7" t="n">
+    <row r="12" ht="12.7" customHeight="1" s="18">
+      <c r="A12" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>0150874683</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>FIGUEROA VIZHNAY DUSHAN XAVIER</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="16" t="n">
         <v>8.65</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="16" t="n">
         <v>8.42</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="16" t="n">
         <v>8.460000000000001</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="16" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="H12" s="9" t="n">
+      <c r="H12" s="16" t="n">
         <v>8.289999999999999</v>
       </c>
-      <c r="I12" s="9" t="n">
+      <c r="I12" s="16" t="n">
         <v>8.56</v>
       </c>
-      <c r="J12" s="9" t="n">
+      <c r="J12" s="16" t="n">
         <v>8.460000000000001</v>
       </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M12" s="9" t="n">
+      <c r="K12" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L12" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M12" s="16" t="n">
         <v>8.529999999999999</v>
       </c>
-      <c r="N12" s="7" t="inlineStr">
+      <c r="N12" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O12" s="7" t="inlineStr">
+      <c r="O12" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="n">
+    <row r="13" ht="12.7" customHeight="1" s="18">
+      <c r="A13" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>0150927986</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>GOMEZ VERA ADRIAN ISMAEL</t>
         </is>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="16" t="n">
         <v>8.76</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="16" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="16" t="n">
         <v>8.9</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" s="16" t="n">
         <v>8.83</v>
       </c>
-      <c r="H13" s="9" t="n">
+      <c r="H13" s="16" t="n">
         <v>8.49</v>
       </c>
-      <c r="I13" s="9" t="n">
+      <c r="I13" s="16" t="n">
         <v>8.98</v>
       </c>
-      <c r="J13" s="9" t="n">
+      <c r="J13" s="16" t="n">
         <v>9.220000000000001</v>
       </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M13" s="9" t="n">
+      <c r="K13" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L13" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M13" s="16" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="N13" s="7" t="inlineStr">
+      <c r="N13" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O13" s="7" t="inlineStr">
+      <c r="O13" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="n">
+    <row r="14" ht="12.7" customHeight="1" s="18">
+      <c r="A14" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>0151077948</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>GONZALES AVILA EMILY MARIA</t>
         </is>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="16" t="n">
         <v>9.449999999999999</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="16" t="n">
         <v>9.69</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="16" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="16" t="n">
         <v>9.6</v>
       </c>
-      <c r="H14" s="9" t="n">
+      <c r="H14" s="16" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="I14" s="9" t="n">
+      <c r="I14" s="16" t="n">
         <v>9.9</v>
       </c>
-      <c r="J14" s="9" t="n">
+      <c r="J14" s="16" t="n">
         <v>9.41</v>
       </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M14" s="9" t="n">
+      <c r="K14" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L14" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M14" s="16" t="n">
         <v>9.56</v>
       </c>
-      <c r="N14" s="7" t="inlineStr">
+      <c r="N14" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O14" s="7" t="inlineStr">
+      <c r="O14" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="n">
+    <row r="15" ht="12.7" customHeight="1" s="18">
+      <c r="A15" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>0151261104</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>GUACHICHULLCA SIAVICHAY MATEO</t>
         </is>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="16" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="16" t="n">
         <v>8.470000000000001</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="16" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="16" t="n">
         <v>8.93</v>
       </c>
-      <c r="H15" s="9" t="n">
+      <c r="H15" s="16" t="n">
         <v>8.789999999999999</v>
       </c>
-      <c r="I15" s="9" t="n">
+      <c r="I15" s="16" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="J15" s="9" t="n">
+      <c r="J15" s="16" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M15" s="9" t="n">
+      <c r="K15" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L15" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M15" s="16" t="n">
         <v>8.68</v>
       </c>
-      <c r="N15" s="7" t="inlineStr">
+      <c r="N15" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O15" s="7" t="inlineStr">
+      <c r="O15" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="n">
+    <row r="16" ht="12.7" customHeight="1" s="18">
+      <c r="A16" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>0151019510</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>GUAMAN PINEDA KELLY ESTEFAN</t>
         </is>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="16" t="n">
         <v>9.390000000000001</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="16" t="n">
         <v>9.52</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="16" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="G16" s="9" t="n">
+      <c r="G16" s="16" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="H16" s="9" t="n">
+      <c r="H16" s="16" t="n">
         <v>9.1</v>
       </c>
-      <c r="I16" s="9" t="n">
+      <c r="I16" s="16" t="n">
         <v>9.41</v>
       </c>
-      <c r="J16" s="9" t="n">
+      <c r="J16" s="16" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M16" s="9" t="n">
+      <c r="K16" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L16" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M16" s="16" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="N16" s="7" t="inlineStr">
+      <c r="N16" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O16" s="7" t="inlineStr">
+      <c r="O16" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="n">
+    <row r="17" ht="12.7" customHeight="1" s="18">
+      <c r="A17" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>0151295409</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>GUARQUILA MEJIA FELIX ADRIAN</t>
         </is>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D17" s="16" t="n">
         <v>8.98</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="16" t="n">
         <v>9.140000000000001</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="16" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G17" s="16" t="n">
         <v>9.34</v>
       </c>
-      <c r="H17" s="9" t="n">
+      <c r="H17" s="16" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="I17" s="16" t="n">
         <v>9.44</v>
       </c>
-      <c r="J17" s="9" t="n">
+      <c r="J17" s="16" t="n">
         <v>8.550000000000001</v>
       </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M17" s="9" t="n">
+      <c r="K17" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L17" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M17" s="16" t="n">
         <v>9.02</v>
       </c>
-      <c r="N17" s="7" t="inlineStr">
+      <c r="N17" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O17" s="7" t="inlineStr">
+      <c r="O17" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="n">
+    <row r="18" ht="12.7" customHeight="1" s="18">
+      <c r="A18" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>0151235777</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>JIMBO QUISCUALTUD RUBY JULIETH</t>
         </is>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="16" t="n">
         <v>8.57</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="16" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="16" t="n">
         <v>8.32</v>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="G18" s="16" t="n">
         <v>8.51</v>
       </c>
-      <c r="H18" s="9" t="n">
+      <c r="H18" s="16" t="n">
         <v>7.47</v>
       </c>
-      <c r="I18" s="9" t="n">
+      <c r="I18" s="16" t="n">
         <v>9.529999999999999</v>
       </c>
-      <c r="J18" s="9" t="n">
+      <c r="J18" s="16" t="n">
         <v>7.71</v>
       </c>
-      <c r="K18" s="7" t="inlineStr">
+      <c r="K18" s="14" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
       </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M18" s="9" t="n">
+      <c r="L18" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M18" s="16" t="n">
         <v>8.34</v>
       </c>
-      <c r="N18" s="7" t="inlineStr">
+      <c r="N18" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O18" s="7" t="inlineStr">
+      <c r="O18" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="n">
+    <row r="19" ht="12.7" customHeight="1" s="18">
+      <c r="A19" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>0151242138</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>LEON SIAVICHAY SAMY ELIZABETH</t>
         </is>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D19" s="16" t="n">
         <v>8.27</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="16" t="n">
         <v>8.56</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="16" t="n">
         <v>8.31</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" s="16" t="n">
         <v>8.470000000000001</v>
       </c>
-      <c r="H19" s="9" t="n">
+      <c r="H19" s="16" t="n">
         <v>8.529999999999999</v>
       </c>
-      <c r="I19" s="9" t="n">
+      <c r="I19" s="16" t="n">
         <v>8.17</v>
       </c>
-      <c r="J19" s="9" t="n">
+      <c r="J19" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="K19" s="7" t="inlineStr">
+      <c r="K19" s="14" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
       </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M19" s="9" t="n">
+      <c r="L19" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M19" s="16" t="n">
         <v>8.33</v>
       </c>
-      <c r="N19" s="7" t="inlineStr">
+      <c r="N19" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O19" s="7" t="inlineStr">
+      <c r="O19" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="n">
+    <row r="20" ht="12.7" customHeight="1" s="18">
+      <c r="A20" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>0151161320</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>LLANGARI LLANGARI MARIA BELEN</t>
         </is>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="16" t="n">
         <v>9.640000000000001</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="16" t="n">
         <v>9.640000000000001</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="16" t="n">
         <v>9.41</v>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G20" s="16" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="H20" s="9" t="n">
+      <c r="H20" s="16" t="n">
         <v>9.1</v>
       </c>
-      <c r="I20" s="9" t="n">
+      <c r="I20" s="16" t="n">
         <v>9.58</v>
       </c>
-      <c r="J20" s="9" t="n">
+      <c r="J20" s="16" t="n">
         <v>9.210000000000001</v>
       </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L20" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M20" s="9" t="n">
+      <c r="K20" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L20" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M20" s="16" t="n">
         <v>9.449999999999999</v>
       </c>
-      <c r="N20" s="7" t="inlineStr">
+      <c r="N20" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O20" s="7" t="inlineStr">
+      <c r="O20" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="n">
+    <row r="21" ht="12.7" customHeight="1" s="18">
+      <c r="A21" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>0151192655</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>LLIGUISACA RIOS JHOAN PAUL</t>
         </is>
       </c>
-      <c r="D21" s="9" t="n">
+      <c r="D21" s="16" t="n">
         <v>8.539999999999999</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="16" t="n">
         <v>9.07</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="16" t="n">
         <v>8.470000000000001</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="16" t="n">
         <v>8.51</v>
       </c>
-      <c r="H21" s="9" t="n">
+      <c r="H21" s="16" t="n">
         <v>7.74</v>
       </c>
-      <c r="I21" s="9" t="n">
+      <c r="I21" s="16" t="n">
         <v>9.16</v>
       </c>
-      <c r="J21" s="9" t="n">
+      <c r="J21" s="16" t="n">
         <v>8.220000000000001</v>
       </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M21" s="9" t="n">
+      <c r="K21" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L21" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M21" s="16" t="n">
         <v>8.529999999999999</v>
       </c>
-      <c r="N21" s="7" t="inlineStr">
+      <c r="N21" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O21" s="7" t="inlineStr">
+      <c r="O21" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="n">
+    <row r="22" ht="12.7" customHeight="1" s="18">
+      <c r="A22" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>0151222742</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>MEJIA ZHINDON BRIGITTE TAMAR</t>
         </is>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="16" t="n">
         <v>7.58</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="16" t="n">
         <v>7.35</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="16" t="n">
         <v>7.68</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="16" t="n">
         <v>7.9</v>
       </c>
-      <c r="H22" s="9" t="n">
+      <c r="H22" s="16" t="n">
         <v>7.22</v>
       </c>
-      <c r="I22" s="9" t="n">
+      <c r="I22" s="16" t="n">
         <v>7.82</v>
       </c>
-      <c r="J22" s="9" t="n">
+      <c r="J22" s="16" t="n">
         <v>8.01</v>
       </c>
-      <c r="K22" s="7" t="inlineStr">
+      <c r="K22" s="14" t="inlineStr">
         <is>
           <t>B+</t>
         </is>
       </c>
-      <c r="L22" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M22" s="9" t="n">
+      <c r="L22" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M22" s="16" t="n">
         <v>7.65</v>
       </c>
-      <c r="N22" s="7" t="inlineStr">
+      <c r="N22" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O22" s="7" t="inlineStr">
+      <c r="O22" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="n">
+    <row r="23" ht="12.7" customHeight="1" s="18">
+      <c r="A23" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>0151101706</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>MENDEZ FAJARDO EDISON SEBASTIAN</t>
         </is>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="16" t="n">
         <v>7.86</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="16" t="n">
         <v>8.09</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="16" t="n">
         <v>8.09</v>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" s="16" t="n">
         <v>8.07</v>
       </c>
-      <c r="H23" s="9" t="n">
+      <c r="H23" s="16" t="n">
         <v>7.33</v>
       </c>
-      <c r="I23" s="9" t="n">
+      <c r="I23" s="16" t="n">
         <v>8.6</v>
       </c>
-      <c r="J23" s="9" t="n">
+      <c r="J23" s="16" t="n">
         <v>7.53</v>
       </c>
-      <c r="K23" s="7" t="inlineStr">
+      <c r="K23" s="14" t="inlineStr">
         <is>
           <t>B+</t>
         </is>
       </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M23" s="9" t="n">
+      <c r="L23" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M23" s="16" t="n">
         <v>7.94</v>
       </c>
-      <c r="N23" s="7" t="inlineStr">
+      <c r="N23" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O23" s="7" t="inlineStr">
+      <c r="O23" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="n">
+    <row r="24" ht="12.7" customHeight="1" s="18">
+      <c r="A24" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>0151240603</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>MENDEZ LANDI ANGEL MAURICIO</t>
         </is>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="16" t="n">
         <v>7.96</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="16" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="16" t="n">
         <v>7.96</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="16" t="n">
         <v>7.93</v>
       </c>
-      <c r="H24" s="9" t="n">
+      <c r="H24" s="16" t="n">
         <v>7.55</v>
       </c>
-      <c r="I24" s="9" t="n">
+      <c r="I24" s="16" t="n">
         <v>8.49</v>
       </c>
-      <c r="J24" s="9" t="n">
+      <c r="J24" s="16" t="n">
         <v>7.27</v>
       </c>
-      <c r="K24" s="7" t="inlineStr">
+      <c r="K24" s="14" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
       </c>
-      <c r="L24" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M24" s="9" t="n">
+      <c r="L24" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M24" s="16" t="n">
         <v>7.89</v>
       </c>
-      <c r="N24" s="7" t="inlineStr">
+      <c r="N24" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O24" s="7" t="inlineStr">
+      <c r="O24" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="7" t="n">
+    <row r="25" ht="12.7" customHeight="1" s="18">
+      <c r="A25" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>0151277688</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>MORA UZHCA KEVIN EDUARDO</t>
         </is>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="16" t="n">
         <v>8.52</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="16" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="16" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="16" t="n">
         <v>8.18</v>
       </c>
-      <c r="H25" s="9" t="n">
+      <c r="H25" s="16" t="n">
         <v>7.31</v>
       </c>
-      <c r="I25" s="9" t="n">
+      <c r="I25" s="16" t="n">
         <v>8.81</v>
       </c>
-      <c r="J25" s="9" t="n">
+      <c r="J25" s="16" t="n">
         <v>8.18</v>
       </c>
-      <c r="K25" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L25" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M25" s="9" t="n">
+      <c r="K25" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L25" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M25" s="16" t="n">
         <v>8.19</v>
       </c>
-      <c r="N25" s="7" t="inlineStr">
+      <c r="N25" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O25" s="7" t="inlineStr">
+      <c r="O25" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="7" t="n">
+    <row r="26" ht="12.7" customHeight="1" s="18">
+      <c r="A26" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>0151187416</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>NAULA BONETE LUIS ADOLFO</t>
         </is>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D26" s="16" t="n">
         <v>8.99</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="16" t="n">
         <v>8.66</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="16" t="n">
         <v>8.82</v>
       </c>
-      <c r="G26" s="9" t="n">
+      <c r="G26" s="16" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="H26" s="9" t="n">
+      <c r="H26" s="16" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="I26" s="9" t="n">
+      <c r="I26" s="16" t="n">
         <v>8.949999999999999</v>
       </c>
-      <c r="J26" s="9" t="n">
+      <c r="J26" s="16" t="n">
         <v>9.109999999999999</v>
       </c>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L26" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M26" s="9" t="n">
+      <c r="K26" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L26" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M26" s="16" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="N26" s="7" t="inlineStr">
+      <c r="N26" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O26" s="7" t="inlineStr">
+      <c r="O26" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="n">
+    <row r="27" ht="12.7" customHeight="1" s="18">
+      <c r="A27" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>0151122223</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="15" t="inlineStr">
         <is>
           <t>PACHECO CAMPOS THIAGO STEEVEN</t>
         </is>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="D27" s="16" t="n">
         <v>8.75</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="16" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="16" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="G27" s="9" t="n">
+      <c r="G27" s="16" t="n">
         <v>8.69</v>
       </c>
-      <c r="H27" s="9" t="n">
+      <c r="H27" s="16" t="n">
         <v>8.470000000000001</v>
       </c>
-      <c r="I27" s="9" t="n">
+      <c r="I27" s="16" t="n">
         <v>8.56</v>
       </c>
-      <c r="J27" s="9" t="n">
+      <c r="J27" s="16" t="n">
         <v>8.49</v>
       </c>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L27" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M27" s="9" t="n">
+      <c r="K27" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L27" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M27" s="16" t="n">
         <v>8.67</v>
       </c>
-      <c r="N27" s="7" t="inlineStr">
+      <c r="N27" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O27" s="7" t="inlineStr">
+      <c r="O27" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
+    <row r="28" ht="12.7" customHeight="1" s="18">
+      <c r="A28" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>0151162070</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>PALMA RODRIGUEZ VICTORIA ANAHI</t>
         </is>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="16" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="16" t="n">
         <v>8.960000000000001</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="16" t="n">
         <v>8.91</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="16" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="H28" s="9" t="n">
+      <c r="H28" s="16" t="n">
         <v>9.34</v>
       </c>
-      <c r="I28" s="9" t="n">
+      <c r="I28" s="16" t="n">
         <v>9.01</v>
       </c>
-      <c r="J28" s="9" t="n">
+      <c r="J28" s="16" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M28" s="9" t="n">
+      <c r="K28" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L28" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M28" s="16" t="n">
         <v>8.99</v>
       </c>
-      <c r="N28" s="7" t="inlineStr">
+      <c r="N28" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O28" s="7" t="inlineStr">
+      <c r="O28" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
+    <row r="29" ht="12.7" customHeight="1" s="18">
+      <c r="A29" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>0150941102</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="15" t="inlineStr">
         <is>
           <t>PEREZ MUÑOZ JUSTIN FERNANDO</t>
         </is>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D29" s="16" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="16" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="16" t="n">
         <v>8.68</v>
       </c>
-      <c r="G29" s="9" t="n">
+      <c r="G29" s="16" t="n">
         <v>9.01</v>
       </c>
-      <c r="H29" s="9" t="n">
+      <c r="H29" s="16" t="n">
         <v>8.44</v>
       </c>
-      <c r="I29" s="9" t="n">
+      <c r="I29" s="16" t="n">
         <v>9.109999999999999</v>
       </c>
-      <c r="J29" s="9" t="n">
+      <c r="J29" s="16" t="n">
         <v>8.289999999999999</v>
       </c>
-      <c r="K29" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L29" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M29" s="9" t="n">
+      <c r="K29" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L29" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M29" s="16" t="n">
         <v>8.76</v>
       </c>
-      <c r="N29" s="7" t="inlineStr">
+      <c r="N29" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O29" s="7" t="inlineStr">
+      <c r="O29" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="7" t="n">
+    <row r="30" ht="12.7" customHeight="1" s="18">
+      <c r="A30" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>0150988301</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="15" t="inlineStr">
         <is>
           <t>PILAMUNGA QUESADA JOSEPH DAVID</t>
         </is>
       </c>
-      <c r="D30" s="9" t="n">
+      <c r="D30" s="16" t="n">
         <v>9.619999999999999</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="16" t="n">
         <v>9.33</v>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" s="16" t="n">
         <v>9.619999999999999</v>
       </c>
-      <c r="G30" s="9" t="n">
+      <c r="G30" s="16" t="n">
         <v>9.619999999999999</v>
       </c>
-      <c r="H30" s="9" t="n">
+      <c r="H30" s="16" t="n">
         <v>9.67</v>
       </c>
-      <c r="I30" s="9" t="n">
+      <c r="I30" s="16" t="n">
         <v>9.84</v>
       </c>
-      <c r="J30" s="9" t="n">
+      <c r="J30" s="16" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K30" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L30" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M30" s="9" t="n">
+      <c r="K30" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L30" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M30" s="16" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="N30" s="7" t="inlineStr">
+      <c r="N30" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O30" s="7" t="inlineStr">
+      <c r="O30" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="n">
+    <row r="31" ht="12.7" customHeight="1" s="18">
+      <c r="A31" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>1150404165</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="15" t="inlineStr">
         <is>
           <t>SANDOVAL ESPINOSA XIMENA LIZBETH</t>
         </is>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="16" t="n">
         <v>9.02</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="16" t="n">
         <v>8.74</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="16" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="G31" s="16" t="n">
         <v>9.24</v>
       </c>
-      <c r="H31" s="9" t="n">
+      <c r="H31" s="16" t="n">
         <v>8.77</v>
       </c>
-      <c r="I31" s="9" t="n">
+      <c r="I31" s="16" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="J31" s="9" t="n">
+      <c r="J31" s="16" t="n">
         <v>9.039999999999999</v>
       </c>
-      <c r="K31" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L31" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M31" s="9" t="n">
+      <c r="K31" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L31" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M31" s="16" t="n">
         <v>9.06</v>
       </c>
-      <c r="N31" s="7" t="inlineStr">
+      <c r="N31" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O31" s="7" t="inlineStr">
+      <c r="O31" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="7" t="n">
+    <row r="32" ht="12.7" customHeight="1" s="18">
+      <c r="A32" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>0151025525</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>SONGOR MUZHA JOSEPH MAURICIO</t>
         </is>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D32" s="16" t="n">
         <v>9.02</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="16" t="n">
         <v>9.279999999999999</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="16" t="n">
         <v>8.99</v>
       </c>
-      <c r="G32" s="9" t="n">
+      <c r="G32" s="16" t="n">
         <v>9.24</v>
       </c>
-      <c r="H32" s="9" t="n">
+      <c r="H32" s="16" t="n">
         <v>9.029999999999999</v>
       </c>
-      <c r="I32" s="9" t="n">
+      <c r="I32" s="16" t="n">
         <v>7.98</v>
       </c>
-      <c r="J32" s="9" t="n">
+      <c r="J32" s="16" t="n">
         <v>8.77</v>
       </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L32" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M32" s="9" t="n">
+      <c r="K32" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L32" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M32" s="16" t="n">
         <v>8.9</v>
       </c>
-      <c r="N32" s="7" t="inlineStr">
+      <c r="N32" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O32" s="7" t="inlineStr">
+      <c r="O32" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="7" t="n">
+    <row r="33" ht="12.7" customHeight="1" s="18">
+      <c r="A33" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>0151244787</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>TADAY SANCHO AMY JAMILETH</t>
         </is>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="D33" s="16" t="n">
         <v>9.220000000000001</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="16" t="n">
         <v>8.73</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="16" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="G33" s="9" t="n">
+      <c r="G33" s="16" t="n">
         <v>9.02</v>
       </c>
-      <c r="H33" s="9" t="n">
+      <c r="H33" s="16" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="I33" s="9" t="n">
+      <c r="I33" s="16" t="n">
         <v>9.57</v>
       </c>
-      <c r="J33" s="9" t="n">
+      <c r="J33" s="16" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="K33" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L33" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M33" s="9" t="n">
+      <c r="K33" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L33" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M33" s="16" t="n">
         <v>8.92</v>
       </c>
-      <c r="N33" s="7" t="inlineStr">
+      <c r="N33" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O33" s="7" t="inlineStr">
+      <c r="O33" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="7" t="n">
+    <row r="34" ht="12.7" customHeight="1" s="18">
+      <c r="A34" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>0151271178</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>TENESACA AMENDAÑO CARLOS MANUEL</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="n">
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>TENESACA AMENDAÑO CARLOS DAVID</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="16" t="n">
         <v>9.9</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="16" t="n">
         <v>9.859999999999999</v>
       </c>
-      <c r="G34" s="9" t="n">
+      <c r="G34" s="16" t="n">
         <v>9.619999999999999</v>
       </c>
-      <c r="H34" s="9" t="n">
+      <c r="H34" s="16" t="n">
         <v>9.48</v>
       </c>
-      <c r="I34" s="9" t="n">
+      <c r="I34" s="16" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="J34" s="9" t="n">
+      <c r="J34" s="16" t="n">
         <v>9.74</v>
       </c>
-      <c r="K34" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L34" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M34" s="9" t="n">
+      <c r="K34" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L34" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M34" s="16" t="n">
         <v>9.74</v>
       </c>
-      <c r="N34" s="7" t="inlineStr">
+      <c r="N34" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O34" s="7" t="inlineStr">
+      <c r="O34" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="7" t="n">
+    <row r="35" ht="12.7" customHeight="1" s="18">
+      <c r="A35" s="13" t="n">
         <v>29</v>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>0151305463</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="15" t="inlineStr">
         <is>
           <t>TONGOMBOL CARCHIPULLA MARIA</t>
         </is>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="16" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="16" t="n">
         <v>9.220000000000001</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="16" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="G35" s="9" t="n">
+      <c r="G35" s="16" t="n">
         <v>9.02</v>
       </c>
-      <c r="H35" s="9" t="n">
+      <c r="H35" s="16" t="n">
         <v>7.97</v>
       </c>
-      <c r="I35" s="9" t="n">
+      <c r="I35" s="16" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="J35" s="9" t="n">
+      <c r="J35" s="16" t="n">
         <v>8.33</v>
       </c>
-      <c r="K35" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L35" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M35" s="9" t="n">
+      <c r="K35" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L35" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M35" s="16" t="n">
         <v>8.84</v>
       </c>
-      <c r="N35" s="7" t="inlineStr">
+      <c r="N35" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O35" s="7" t="inlineStr">
+      <c r="O35" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="7" t="n">
+    <row r="36" ht="12.7" customHeight="1" s="18">
+      <c r="A36" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>0151054442</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="15" t="inlineStr">
         <is>
           <t>VELIZ CARRION MELVIN JOEL</t>
         </is>
       </c>
-      <c r="D36" s="9" t="n">
+      <c r="D36" s="16" t="n">
         <v>8.960000000000001</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="16" t="n">
         <v>8.75</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="16" t="n">
         <v>9.07</v>
       </c>
-      <c r="G36" s="9" t="n">
+      <c r="G36" s="16" t="n">
         <v>8.960000000000001</v>
       </c>
-      <c r="H36" s="9" t="n">
+      <c r="H36" s="16" t="n">
         <v>8.74</v>
       </c>
-      <c r="I36" s="9" t="n">
+      <c r="I36" s="16" t="n">
         <v>9.6</v>
       </c>
-      <c r="J36" s="9" t="n">
+      <c r="J36" s="16" t="n">
         <v>8.630000000000001</v>
       </c>
-      <c r="K36" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L36" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M36" s="9" t="n">
+      <c r="K36" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L36" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M36" s="16" t="n">
         <v>8.960000000000001</v>
       </c>
-      <c r="N36" s="7" t="inlineStr">
+      <c r="N36" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O36" s="7" t="inlineStr">
+      <c r="O36" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="7" t="n">
+    <row r="37" ht="12.7" customHeight="1" s="18">
+      <c r="A37" s="13" t="n">
         <v>31</v>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>0151126836</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="15" t="inlineStr">
         <is>
           <t>VIVEROS BRITO MATIAS JAVIER</t>
         </is>
       </c>
-      <c r="D37" s="9" t="n">
+      <c r="D37" s="16" t="n">
         <v>8.74</v>
       </c>
-      <c r="E37" s="9" t="n">
+      <c r="E37" s="16" t="n">
         <v>9.35</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="16" t="n">
         <v>8.640000000000001</v>
       </c>
-      <c r="G37" s="9" t="n">
+      <c r="G37" s="16" t="n">
         <v>8.789999999999999</v>
       </c>
-      <c r="H37" s="9" t="n">
+      <c r="H37" s="16" t="n">
         <v>8.08</v>
       </c>
-      <c r="I37" s="9" t="n">
+      <c r="I37" s="16" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="J37" s="9" t="n">
+      <c r="J37" s="16" t="n">
         <v>8.619999999999999</v>
       </c>
-      <c r="K37" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L37" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M37" s="9" t="n">
+      <c r="K37" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L37" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M37" s="16" t="n">
         <v>8.789999999999999</v>
       </c>
-      <c r="N37" s="7" t="inlineStr">
+      <c r="N37" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O37" s="7" t="inlineStr">
+      <c r="O37" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="7" t="n">
+    <row r="38" ht="12.7" customHeight="1" s="18">
+      <c r="A38" s="13" t="n">
         <v>32</v>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>0150929750</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="15" t="inlineStr">
         <is>
           <t>VIZHÑAY CEDACERO DAYSI ANAI</t>
         </is>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="D38" s="16" t="n">
         <v>9.369999999999999</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="16" t="n">
         <v>9.529999999999999</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="16" t="n">
         <v>9.32</v>
       </c>
-      <c r="G38" s="9" t="n">
+      <c r="G38" s="16" t="n">
         <v>9.74</v>
       </c>
-      <c r="H38" s="9" t="n">
+      <c r="H38" s="16" t="n">
         <v>9.84</v>
       </c>
-      <c r="I38" s="9" t="n">
+      <c r="I38" s="16" t="n">
         <v>9.81</v>
       </c>
-      <c r="J38" s="9" t="n">
+      <c r="J38" s="16" t="n">
         <v>9.279999999999999</v>
       </c>
-      <c r="K38" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L38" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M38" s="9" t="n">
+      <c r="K38" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L38" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M38" s="16" t="n">
         <v>9.56</v>
       </c>
-      <c r="N38" s="7" t="inlineStr">
+      <c r="N38" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O38" s="7" t="inlineStr">
+      <c r="O38" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="7" t="n">
+    <row r="39" ht="12.7" customHeight="1" s="18">
+      <c r="A39" s="13" t="n">
         <v>33</v>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>0151130176</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="15" t="inlineStr">
         <is>
           <t>ZHUNGO MOROCHO DANIEL MAXIMILIANO</t>
         </is>
       </c>
-      <c r="D39" s="9" t="n">
+      <c r="D39" s="16" t="n">
         <v>8.23</v>
       </c>
-      <c r="E39" s="9" t="n">
+      <c r="E39" s="16" t="n">
         <v>8.18</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="16" t="n">
         <v>8.460000000000001</v>
       </c>
-      <c r="G39" s="9" t="n">
+      <c r="G39" s="16" t="n">
         <v>8.43</v>
       </c>
-      <c r="H39" s="9" t="n">
+      <c r="H39" s="16" t="n">
         <v>8.27</v>
       </c>
-      <c r="I39" s="9" t="n">
+      <c r="I39" s="16" t="n">
         <v>8.720000000000001</v>
       </c>
-      <c r="J39" s="9" t="n">
+      <c r="J39" s="16" t="n">
         <v>9.02</v>
       </c>
-      <c r="K39" s="7" t="inlineStr">
+      <c r="K39" s="14" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
       </c>
-      <c r="L39" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M39" s="9" t="n">
+      <c r="L39" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M39" s="16" t="n">
         <v>8.470000000000001</v>
       </c>
-      <c r="N39" s="7" t="inlineStr">
+      <c r="N39" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O39" s="7" t="inlineStr">
+      <c r="O39" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="7" t="n">
+    <row r="40" ht="12.7" customHeight="1" s="18">
+      <c r="A40" s="13" t="n">
         <v>34</v>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>0151150844</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" s="15" t="inlineStr">
         <is>
           <t>ZUÑIGA UZHCA ANGEL SAMUEL</t>
         </is>
       </c>
-      <c r="D40" s="9" t="n">
+      <c r="D40" s="16" t="n">
         <v>8.16</v>
       </c>
-      <c r="E40" s="9" t="n">
+      <c r="E40" s="16" t="n">
         <v>8.25</v>
       </c>
-      <c r="F40" s="9" t="n">
+      <c r="F40" s="16" t="n">
         <v>8.34</v>
       </c>
-      <c r="G40" s="9" t="n">
+      <c r="G40" s="16" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="H40" s="9" t="n">
+      <c r="H40" s="16" t="n">
         <v>7.89</v>
       </c>
-      <c r="I40" s="9" t="n">
+      <c r="I40" s="16" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="J40" s="9" t="n">
+      <c r="J40" s="16" t="n">
         <v>7.95</v>
       </c>
-      <c r="K40" s="7" t="inlineStr">
+      <c r="K40" s="14" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
       </c>
-      <c r="L40" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M40" s="9" t="n">
+      <c r="L40" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M40" s="16" t="n">
         <v>8.18</v>
       </c>
-      <c r="N40" s="7" t="inlineStr">
+      <c r="N40" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O40" s="7" t="inlineStr">
+      <c r="O40" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="7" t="n">
+    <row r="41" ht="12.7" customHeight="1" s="18">
+      <c r="A41" s="13" t="n">
         <v>35</v>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>0150852705</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="15" t="inlineStr">
         <is>
           <t>ÑAUTA CAGUANA BYRON STEVEN</t>
         </is>
       </c>
-      <c r="D41" s="9" t="n">
+      <c r="D41" s="16" t="n">
         <v>9.85</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="E41" s="16" t="n">
         <v>9.83</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="16" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="G41" s="9" t="n">
+      <c r="G41" s="16" t="n">
         <v>9.66</v>
       </c>
-      <c r="H41" s="9" t="n">
+      <c r="H41" s="16" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="I41" s="9" t="n">
+      <c r="I41" s="16" t="n">
         <v>9.92</v>
       </c>
-      <c r="J41" s="9" t="n">
+      <c r="J41" s="16" t="n">
         <v>9.529999999999999</v>
       </c>
-      <c r="K41" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="L41" s="7" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M41" s="9" t="n">
+      <c r="K41" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="L41" s="14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M41" s="16" t="n">
         <v>9.76</v>
       </c>
-      <c r="N41" s="7" t="inlineStr">
+      <c r="N41" s="14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O41" s="7" t="inlineStr">
+      <c r="O41" s="14" t="inlineStr">
         <is>
           <t>PROMOVIDO</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="12" t="n"/>
-      <c r="D42" s="10" t="n">
+    <row r="42" ht="13.55" customHeight="1" s="18">
+      <c r="A42" s="7" t="n"/>
+      <c r="B42" s="21" t="n"/>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="17" t="n">
         <v>309.34</v>
       </c>
-      <c r="E42" s="10" t="n">
+      <c r="E42" s="17" t="n">
         <v>308.96</v>
       </c>
-      <c r="F42" s="10" t="n">
+      <c r="F42" s="17" t="n">
         <v>308.69</v>
       </c>
-      <c r="G42" s="10" t="n">
+      <c r="G42" s="17" t="n">
         <v>311.67</v>
       </c>
-      <c r="H42" s="10" t="n">
+      <c r="H42" s="17" t="n">
         <v>298.21</v>
       </c>
-      <c r="I42" s="10" t="n">
+      <c r="I42" s="17" t="n">
         <v>317.83</v>
       </c>
-      <c r="J42" s="10" t="n">
+      <c r="J42" s="17" t="n">
         <v>304.51</v>
       </c>
-      <c r="K42" s="4" t="n"/>
-      <c r="L42" s="5" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="M42" s="10" t="n">
+      <c r="K42" s="7" t="n"/>
+      <c r="L42" s="8" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M42" s="17" t="n">
         <v>308.46</v>
       </c>
-      <c r="N42" s="4" t="n"/>
-      <c r="O42" s="4" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="n"/>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="12" t="n"/>
-      <c r="D43" s="10" t="n">
+      <c r="N42" s="7" t="n"/>
+      <c r="O42" s="7" t="n"/>
+    </row>
+    <row r="43" ht="13.55" customHeight="1" s="18">
+      <c r="A43" s="7" t="n"/>
+      <c r="B43" s="21" t="n"/>
+      <c r="C43" s="22" t="n"/>
+      <c r="D43" s="17" t="n">
         <v>8.84</v>
       </c>
-      <c r="E43" s="10" t="n">
+      <c r="E43" s="17" t="n">
         <v>8.83</v>
       </c>
-      <c r="F43" s="10" t="n">
+      <c r="F43" s="17" t="n">
         <v>8.82</v>
       </c>
-      <c r="G43" s="10" t="n">
+      <c r="G43" s="17" t="n">
         <v>8.9</v>
       </c>
-      <c r="H43" s="10" t="n">
+      <c r="H43" s="17" t="n">
         <v>8.52</v>
       </c>
-      <c r="I43" s="10" t="n">
+      <c r="I43" s="17" t="n">
         <v>9.08</v>
       </c>
-      <c r="J43" s="10" t="n">
+      <c r="J43" s="17" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="K43" s="4" t="n"/>
-      <c r="L43" s="4" t="n"/>
-      <c r="M43" s="10" t="n">
+      <c r="K43" s="7" t="n"/>
+      <c r="L43" s="7" t="n"/>
+      <c r="M43" s="17" t="n">
         <v>8.81</v>
       </c>
-      <c r="N43" s="4" t="n"/>
-      <c r="O43" s="4" t="n"/>
+      <c r="N43" s="7" t="n"/>
+      <c r="O43" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -3309,5 +3884,14 @@
     <mergeCell ref="A3:O3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>